--- a/forms/trg/Formulir_TRG_res-economics.xlsx
+++ b/forms/trg/Formulir_TRG_res-economics.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B44)</f>
+        <f>COUNTA(Anggota!B5:B45)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F44)</f>
+        <f>COUNTA(Anggota!F5:F45)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,27 +913,31 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Ismail Kadir H. Palladjarang</t>
+          <t>Rahmatia</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="n"/>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="12" t="n"/>
-      <c r="K5" s="12" t="n"/>
-      <c r="L5" s="12" t="n"/>
+      <c r="K5" s="11" t="inlineStr">
+        <is>
+          <t>6030864</t>
+        </is>
+      </c>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>57212136064</t>
+        </is>
+      </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -946,12 +950,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Rusda</t>
+          <t>Ismail Kadir H. Palladjarang</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -979,12 +983,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Ayu Latifah Alfisyahrin</t>
+          <t>Rusda</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -997,21 +1001,9 @@
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="12" t="n"/>
       <c r="I7" s="12" t="n"/>
-      <c r="J7" s="11" t="inlineStr">
-        <is>
-          <t>0009-0005-3106-6269</t>
-        </is>
-      </c>
-      <c r="K7" s="11" t="inlineStr">
-        <is>
-          <t>6857292</t>
-        </is>
-      </c>
-      <c r="L7" s="11" t="inlineStr">
-        <is>
-          <t>59405921400</t>
-        </is>
-      </c>
+      <c r="J7" s="12" t="n"/>
+      <c r="K7" s="12" t="n"/>
+      <c r="L7" s="12" t="n"/>
       <c r="M7" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1024,12 +1016,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Amanus Khalifah Fil’ardy Yunus</t>
+          <t>Ayu Latifah Alfisyahrin</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1042,15 +1034,19 @@
       <c r="G8" s="12" t="n"/>
       <c r="H8" s="12" t="n"/>
       <c r="I8" s="12" t="n"/>
-      <c r="J8" s="12" t="n"/>
+      <c r="J8" s="11" t="inlineStr">
+        <is>
+          <t>0009-0005-3106-6269</t>
+        </is>
+      </c>
       <c r="K8" s="11" t="inlineStr">
         <is>
-          <t>6030892</t>
+          <t>6857292</t>
         </is>
       </c>
       <c r="L8" s="11" t="inlineStr">
         <is>
-          <t>57216866137</t>
+          <t>59405921400</t>
         </is>
       </c>
       <c r="M8" s="11" t="inlineStr">
@@ -1065,12 +1061,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Nur Dwiana Sari Saudi</t>
+          <t>Amanus Khalifah Fil’ardy Yunus</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1086,12 +1082,12 @@
       <c r="J9" s="12" t="n"/>
       <c r="K9" s="11" t="inlineStr">
         <is>
-          <t>6031958</t>
+          <t>6030892</t>
         </is>
       </c>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>57208471228</t>
+          <t>57216866137</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
@@ -1106,12 +1102,12 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Sabir</t>
+          <t>Nur Dwiana Sari Saudi</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1127,12 +1123,12 @@
       <c r="J10" s="12" t="n"/>
       <c r="K10" s="11" t="inlineStr">
         <is>
-          <t>6082874</t>
+          <t>6031958</t>
         </is>
       </c>
       <c r="L10" s="11" t="inlineStr">
         <is>
-          <t>57216620122</t>
+          <t>57208471228</t>
         </is>
       </c>
       <c r="M10" s="11" t="inlineStr">
@@ -1147,12 +1143,12 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Hamrullah</t>
+          <t>Sabir</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1168,10 +1164,14 @@
       <c r="J11" s="12" t="n"/>
       <c r="K11" s="11" t="inlineStr">
         <is>
-          <t>6031578</t>
-        </is>
-      </c>
-      <c r="L11" s="12" t="n"/>
+          <t>6082874</t>
+        </is>
+      </c>
+      <c r="L11" s="11" t="inlineStr">
+        <is>
+          <t>57216620122</t>
+        </is>
+      </c>
       <c r="M11" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Madris</t>
+          <t>Hamrullah</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1205,14 +1205,10 @@
       <c r="J12" s="12" t="n"/>
       <c r="K12" s="11" t="inlineStr">
         <is>
-          <t>6039189</t>
-        </is>
-      </c>
-      <c r="L12" s="11" t="inlineStr">
-        <is>
-          <t>57207466871</t>
-        </is>
-      </c>
+          <t>6031578</t>
+        </is>
+      </c>
+      <c r="L12" s="12" t="n"/>
       <c r="M12" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1225,12 +1221,12 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Sanusi Fattah</t>
+          <t>Madris</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1246,12 +1242,12 @@
       <c r="J13" s="12" t="n"/>
       <c r="K13" s="11" t="inlineStr">
         <is>
-          <t>6026195</t>
+          <t>6039189</t>
         </is>
       </c>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>57193409887</t>
+          <t>57207466871</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
@@ -1266,12 +1262,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Akbar Mandela Arumatulabala Yunus</t>
+          <t>Sanusi Fattah</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1287,12 +1283,12 @@
       <c r="J14" s="12" t="n"/>
       <c r="K14" s="11" t="inlineStr">
         <is>
-          <t>6747970</t>
+          <t>6026195</t>
         </is>
       </c>
       <c r="L14" s="11" t="inlineStr">
         <is>
-          <t>59333838300</t>
+          <t>57193409887</t>
         </is>
       </c>
       <c r="M14" s="11" t="inlineStr">
@@ -1307,12 +1303,12 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Munawwarah S. Mubarak</t>
+          <t>Akbar Mandela Arumatulabala Yunus</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -1328,12 +1324,12 @@
       <c r="J15" s="12" t="n"/>
       <c r="K15" s="11" t="inlineStr">
         <is>
-          <t>6047617</t>
+          <t>6747970</t>
         </is>
       </c>
       <c r="L15" s="11" t="inlineStr">
         <is>
-          <t>59334370000</t>
+          <t>59333838300</t>
         </is>
       </c>
       <c r="M15" s="11" t="inlineStr">
@@ -1348,12 +1344,12 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Hasmin</t>
+          <t>Munawwarah S. Mubarak</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
@@ -1369,12 +1365,12 @@
       <c r="J16" s="12" t="n"/>
       <c r="K16" s="11" t="inlineStr">
         <is>
-          <t>6011314</t>
+          <t>6047617</t>
         </is>
       </c>
       <c r="L16" s="11" t="inlineStr">
         <is>
-          <t>57207449718</t>
+          <t>59334370000</t>
         </is>
       </c>
       <c r="M16" s="11" t="inlineStr">
@@ -1389,17 +1385,17 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Khalid Eltayeb Elfaki</t>
+          <t>Hasmin</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>University of Gezira</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E17" s="11" t="n"/>
@@ -1407,15 +1403,15 @@
       <c r="G17" s="12" t="n"/>
       <c r="H17" s="12" t="n"/>
       <c r="I17" s="12" t="n"/>
-      <c r="J17" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-8728-0492</t>
-        </is>
-      </c>
-      <c r="K17" s="12" t="n"/>
+      <c r="J17" s="12" t="n"/>
+      <c r="K17" s="11" t="inlineStr">
+        <is>
+          <t>6011314</t>
+        </is>
+      </c>
       <c r="L17" s="11" t="inlineStr">
         <is>
-          <t>57203807123</t>
+          <t>57207449718</t>
         </is>
       </c>
       <c r="M17" s="11" t="inlineStr">
@@ -1430,17 +1426,17 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Valentin Laura Sampe</t>
+          <t>Khalid Eltayeb Elfaki</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>Politeknik STIA LAN Makassar</t>
+          <t>University of Gezira</t>
         </is>
       </c>
       <c r="E18" s="11" t="n"/>
@@ -1448,9 +1444,17 @@
       <c r="G18" s="12" t="n"/>
       <c r="H18" s="12" t="n"/>
       <c r="I18" s="12" t="n"/>
-      <c r="J18" s="12" t="n"/>
+      <c r="J18" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-8728-0492</t>
+        </is>
+      </c>
       <c r="K18" s="12" t="n"/>
-      <c r="L18" s="12" t="n"/>
+      <c r="L18" s="11" t="inlineStr">
+        <is>
+          <t>57203807123</t>
+        </is>
+      </c>
       <c r="M18" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1463,17 +1467,17 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Fara Triadi</t>
+          <t>Valentin Laura Sampe</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Politeknik Negeri Samarinda</t>
+          <t>Politeknik STIA LAN Makassar</t>
         </is>
       </c>
       <c r="E19" s="11" t="n"/>
@@ -1482,16 +1486,8 @@
       <c r="H19" s="12" t="n"/>
       <c r="I19" s="12" t="n"/>
       <c r="J19" s="12" t="n"/>
-      <c r="K19" s="11" t="inlineStr">
-        <is>
-          <t>6904835</t>
-        </is>
-      </c>
-      <c r="L19" s="11" t="inlineStr">
-        <is>
-          <t>58139887500</t>
-        </is>
-      </c>
+      <c r="K19" s="12" t="n"/>
+      <c r="L19" s="12" t="n"/>
       <c r="M19" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1504,17 +1500,17 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>Adinda Asiah Minhikmah Alena Pituleng Yunus</t>
+          <t>Fara Triadi</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>Universitas Pembangunan Nasional Veteran Jakarta</t>
+          <t>Politeknik Negeri Samarinda</t>
         </is>
       </c>
       <c r="E20" s="11" t="n"/>
@@ -1523,8 +1519,16 @@
       <c r="H20" s="12" t="n"/>
       <c r="I20" s="12" t="n"/>
       <c r="J20" s="12" t="n"/>
-      <c r="K20" s="12" t="n"/>
-      <c r="L20" s="12" t="n"/>
+      <c r="K20" s="11" t="inlineStr">
+        <is>
+          <t>6904835</t>
+        </is>
+      </c>
+      <c r="L20" s="11" t="inlineStr">
+        <is>
+          <t>58139887500</t>
+        </is>
+      </c>
       <c r="M20" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1537,17 +1541,17 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>Martha Edward Makatha</t>
+          <t>Adinda Asiah Minhikmah Alena Pituleng Yunus</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>Tanzania Institute of Accountancy</t>
+          <t>Universitas Pembangunan Nasional Veteran Jakarta</t>
         </is>
       </c>
       <c r="E21" s="11" t="n"/>
@@ -1555,11 +1559,7 @@
       <c r="G21" s="12" t="n"/>
       <c r="H21" s="12" t="n"/>
       <c r="I21" s="12" t="n"/>
-      <c r="J21" s="11" t="inlineStr">
-        <is>
-          <t>0009-0009-6040-2873</t>
-        </is>
-      </c>
+      <c r="J21" s="12" t="n"/>
       <c r="K21" s="12" t="n"/>
       <c r="L21" s="12" t="n"/>
       <c r="M21" s="11" t="inlineStr">
@@ -1574,21 +1574,29 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>Ahmad Amir</t>
+          <t>Martha Edward Makatha</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="n"/>
+          <t>External collaborator</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>Tanzania Institute of Accountancy</t>
+        </is>
+      </c>
       <c r="E22" s="11" t="n"/>
       <c r="F22" s="12" t="n"/>
       <c r="G22" s="12" t="n"/>
       <c r="H22" s="12" t="n"/>
       <c r="I22" s="12" t="n"/>
-      <c r="J22" s="12" t="n"/>
+      <c r="J22" s="11" t="inlineStr">
+        <is>
+          <t>0009-0009-6040-2873</t>
+        </is>
+      </c>
       <c r="K22" s="12" t="n"/>
       <c r="L22" s="12" t="n"/>
       <c r="M22" s="11" t="inlineStr">
@@ -1603,12 +1611,12 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>Andi Muhammad Ichwan Pananrangi</t>
+          <t>Ahmad Amir</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D23" s="12" t="n"/>
@@ -1632,12 +1640,12 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>Feral Eka Maya Dwipa</t>
+          <t>Andi Muhammad Ichwan Pananrangi</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D24" s="12" t="n"/>
@@ -1661,12 +1669,12 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>Alamsyah Amiruddin</t>
+          <t>Feral Eka Maya Dwipa</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D25" s="12" t="n"/>
@@ -1690,12 +1698,12 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Hilal Mubarak</t>
+          <t>Alamsyah Amiruddin</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D26" s="12" t="n"/>
@@ -1719,12 +1727,12 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>Khadijatul Fatiyah Mubarak</t>
+          <t>Muhammad Hilal Mubarak</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D27" s="12" t="n"/>
@@ -1735,11 +1743,7 @@
       <c r="I27" s="12" t="n"/>
       <c r="J27" s="12" t="n"/>
       <c r="K27" s="12" t="n"/>
-      <c r="L27" s="11" t="inlineStr">
-        <is>
-          <t>59205876900</t>
-        </is>
-      </c>
+      <c r="L27" s="12" t="n"/>
       <c r="M27" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1752,19 +1756,15 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>Laurenz Thiele</t>
+          <t>Khadijatul Fatiyah Mubarak</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
-        </is>
-      </c>
-      <c r="D28" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
+          <t>Researcher</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="n"/>
       <c r="E28" s="11" t="n"/>
       <c r="F28" s="12" t="n"/>
       <c r="G28" s="12" t="n"/>
@@ -1772,7 +1772,11 @@
       <c r="I28" s="12" t="n"/>
       <c r="J28" s="12" t="n"/>
       <c r="K28" s="12" t="n"/>
-      <c r="L28" s="12" t="n"/>
+      <c r="L28" s="11" t="inlineStr">
+        <is>
+          <t>59205876900</t>
+        </is>
+      </c>
       <c r="M28" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1785,12 +1789,12 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>Oktavianty</t>
+          <t>Laurenz Thiele</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
@@ -1818,12 +1822,12 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>Armin Amri</t>
+          <t>Oktavianty</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
@@ -1851,12 +1855,12 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Ridwan Manulusi</t>
+          <t>Armin Amri</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
@@ -1884,12 +1888,12 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>Anas Iswanto Anwar</t>
+          <t>Muhammad Ridwan Manulusi</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
@@ -1897,22 +1901,18 @@
           <t>Hasanuddin University</t>
         </is>
       </c>
-      <c r="E32" s="11" t="n"/>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>The Resource Economics Research Group is dedicated to exploring sustainable and equitable solutions for resource utilization in achieving economic growth. In response to increasing resource scarcity and environmental challenges, we integrate economic theories, empirical research, and multidisciplinary collaboration to develop innovative strategies for optimal resource management. Our mission is to provide evidence-based insights, policy recommendations, and practical solutions that balance economic prosperity with environmental sustainability. By fostering collaboration with academic, governmental, and industrial stakeholders, we aim to drive impactful research that supports long-term economic resilience and responsible resource use for future generations.</t>
+        </is>
+      </c>
       <c r="F32" s="12" t="n"/>
       <c r="G32" s="12" t="n"/>
       <c r="H32" s="12" t="n"/>
       <c r="I32" s="12" t="n"/>
       <c r="J32" s="12" t="n"/>
-      <c r="K32" s="11" t="inlineStr">
-        <is>
-          <t>6012273</t>
-        </is>
-      </c>
-      <c r="L32" s="11" t="inlineStr">
-        <is>
-          <t>57614523400</t>
-        </is>
-      </c>
+      <c r="K32" s="12" t="n"/>
+      <c r="L32" s="12" t="n"/>
       <c r="M32" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1923,18 +1923,42 @@
       <c r="A33" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="12" t="n"/>
-      <c r="C33" s="12" t="n"/>
-      <c r="D33" s="12" t="n"/>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>Anas Iswanto Anwar</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
       <c r="E33" s="11" t="n"/>
       <c r="F33" s="12" t="n"/>
       <c r="G33" s="12" t="n"/>
       <c r="H33" s="12" t="n"/>
       <c r="I33" s="12" t="n"/>
       <c r="J33" s="12" t="n"/>
-      <c r="K33" s="12" t="n"/>
-      <c r="L33" s="12" t="n"/>
-      <c r="M33" s="12" t="n"/>
+      <c r="K33" s="11" t="inlineStr">
+        <is>
+          <t>6012273</t>
+        </is>
+      </c>
+      <c r="L33" s="11" t="inlineStr">
+        <is>
+          <t>57614523400</t>
+        </is>
+      </c>
+      <c r="M33" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
@@ -2123,15 +2147,32 @@
       <c r="L44" s="12" t="n"/>
       <c r="M44" s="12" t="n"/>
     </row>
+    <row r="45">
+      <c r="A45" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="B45" s="12" t="n"/>
+      <c r="C45" s="12" t="n"/>
+      <c r="D45" s="12" t="n"/>
+      <c r="E45" s="11" t="n"/>
+      <c r="F45" s="12" t="n"/>
+      <c r="G45" s="12" t="n"/>
+      <c r="H45" s="12" t="n"/>
+      <c r="I45" s="12" t="n"/>
+      <c r="J45" s="12" t="n"/>
+      <c r="K45" s="12" t="n"/>
+      <c r="L45" s="12" t="n"/>
+      <c r="M45" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
